--- a/navneleg-demo/fruit-vegetables/frugt_groent_flersproget_demo.xlsx
+++ b/navneleg-demo/fruit-vegetables/frugt_groent_flersproget_demo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frugt og grønt" sheetId="1" r:id="R555db6cd782e4910"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frugt og grønt" sheetId="1" r:id="R2fd7fd9e3c9344bc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1D4ED8"/>
+        <x:fgColor rgb="FF2563EB"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -78,24 +78,6 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FrugtoggrntTable" displayName="FrugtoggrntTable" ref="A1:J26" headerRowCount="1">
-  <x:tableColumns count="10">
-    <x:tableColumn id="1" name="KortID"/>
-    <x:tableColumn id="2" name="Billedfil"/>
-    <x:tableColumn id="3" name="Billedsti"/>
-    <x:tableColumn id="4" name="Dansk"/>
-    <x:tableColumn id="5" name="English"/>
-    <x:tableColumn id="6" name="Deutsch"/>
-    <x:tableColumn id="7" name="Français"/>
-    <x:tableColumn id="8" name="Español"/>
-    <x:tableColumn id="9" name="Kategori"/>
-    <x:tableColumn id="10" name="Hint"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -247,19 +229,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="32" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="6" t="str">
         <x:v>KortID</x:v>
       </x:c>
@@ -270,24 +253,27 @@
         <x:v>Billedsti</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
+        <x:v>Forside</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
         <x:v>Dansk</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>English</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>Deutsch</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>Français</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="I1" s="6" t="str">
         <x:v>Español</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="J1" s="6" t="str">
         <x:v>Kategori</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="K1" s="6" t="str">
         <x:v>Hint</x:v>
       </x:c>
     </x:row>
@@ -305,21 +291,24 @@
         <x:v>Æble</x:v>
       </x:c>
       <x:c r="E2" s="12" t="str">
+        <x:v>Æble</x:v>
+      </x:c>
+      <x:c r="F2" s="12" t="str">
         <x:v>Apple</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="G2" s="12" t="str">
         <x:v>Apfel</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="H2" s="12" t="str">
         <x:v>Pomme</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="I2" s="12" t="str">
         <x:v>Manzana</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="J2" s="12" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="K2" s="12" t="str">
         <x:v>Æble er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -337,7 +326,7 @@
         <x:v>Appelsin</x:v>
       </x:c>
       <x:c r="E3" s="12" t="str">
-        <x:v>Orange</x:v>
+        <x:v>Appelsin</x:v>
       </x:c>
       <x:c r="F3" s="12" t="str">
         <x:v>Orange</x:v>
@@ -346,12 +335,15 @@
         <x:v>Orange</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
+        <x:v>Orange</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="str">
         <x:v>Naranja</x:v>
       </x:c>
-      <x:c r="I3" s="12" t="str">
+      <x:c r="J3" s="12" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="J3" s="12" t="str">
+      <x:c r="K3" s="12" t="str">
         <x:v>Appelsin er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -369,21 +361,24 @@
         <x:v>Banan</x:v>
       </x:c>
       <x:c r="E4" s="12" t="str">
+        <x:v>Banan</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="str">
         <x:v>Banana</x:v>
-      </x:c>
-      <x:c r="F4" s="12" t="str">
-        <x:v>Banane</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
         <x:v>Banane</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
+        <x:v>Banane</x:v>
+      </x:c>
+      <x:c r="I4" s="12" t="str">
         <x:v>Plátano</x:v>
       </x:c>
-      <x:c r="I4" s="12" t="str">
+      <x:c r="J4" s="12" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="J4" s="12" t="str">
+      <x:c r="K4" s="12" t="str">
         <x:v>Banan er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -401,21 +396,24 @@
         <x:v>Jordbær</x:v>
       </x:c>
       <x:c r="E5" s="12" t="str">
+        <x:v>Jordbær</x:v>
+      </x:c>
+      <x:c r="F5" s="12" t="str">
         <x:v>Strawberry</x:v>
       </x:c>
-      <x:c r="F5" s="12" t="str">
+      <x:c r="G5" s="12" t="str">
         <x:v>Erdbeere</x:v>
       </x:c>
-      <x:c r="G5" s="12" t="str">
+      <x:c r="H5" s="12" t="str">
         <x:v>Fraise</x:v>
       </x:c>
-      <x:c r="H5" s="12" t="str">
+      <x:c r="I5" s="12" t="str">
         <x:v>Fresa</x:v>
       </x:c>
-      <x:c r="I5" s="12" t="str">
+      <x:c r="J5" s="12" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="J5" s="12" t="str">
+      <x:c r="K5" s="12" t="str">
         <x:v>Jordbær er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -433,21 +431,24 @@
         <x:v>Pære</x:v>
       </x:c>
       <x:c r="E6" s="12" t="str">
+        <x:v>Pære</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
         <x:v>Pear</x:v>
       </x:c>
-      <x:c r="F6" s="12" t="str">
+      <x:c r="G6" s="12" t="str">
         <x:v>Birne</x:v>
       </x:c>
-      <x:c r="G6" s="12" t="str">
+      <x:c r="H6" s="12" t="str">
         <x:v>Poire</x:v>
       </x:c>
-      <x:c r="H6" s="12" t="str">
+      <x:c r="I6" s="12" t="str">
         <x:v>Pera</x:v>
       </x:c>
-      <x:c r="I6" s="12" t="str">
+      <x:c r="J6" s="12" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="J6" s="12" t="str">
+      <x:c r="K6" s="12" t="str">
         <x:v>Pære er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -465,21 +466,24 @@
         <x:v>Vindruer</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
+        <x:v>Vindruer</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="str">
         <x:v>Grapes</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="str">
+      <x:c r="G7" s="12" t="str">
         <x:v>Trauben</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="str">
+      <x:c r="H7" s="12" t="str">
         <x:v>Raisins</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="str">
+      <x:c r="I7" s="12" t="str">
         <x:v>Uvas</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="str">
+      <x:c r="J7" s="12" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="str">
+      <x:c r="K7" s="12" t="str">
         <x:v>Vindruer er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -497,21 +501,24 @@
         <x:v>Ananas</x:v>
       </x:c>
       <x:c r="E8" s="12" t="str">
+        <x:v>Ananas</x:v>
+      </x:c>
+      <x:c r="F8" s="12" t="str">
         <x:v>Pineapple</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="str">
-        <x:v>Ananas</x:v>
       </x:c>
       <x:c r="G8" s="12" t="str">
         <x:v>Ananas</x:v>
       </x:c>
       <x:c r="H8" s="12" t="str">
+        <x:v>Ananas</x:v>
+      </x:c>
+      <x:c r="I8" s="12" t="str">
         <x:v>Piña</x:v>
       </x:c>
-      <x:c r="I8" s="12" t="str">
+      <x:c r="J8" s="12" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="str">
+      <x:c r="K8" s="12" t="str">
         <x:v>Ananas er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -529,21 +536,24 @@
         <x:v>Vandmelon</x:v>
       </x:c>
       <x:c r="E9" s="12" t="str">
+        <x:v>Vandmelon</x:v>
+      </x:c>
+      <x:c r="F9" s="12" t="str">
         <x:v>Watermelon</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="str">
+      <x:c r="G9" s="12" t="str">
         <x:v>Wassermelone</x:v>
       </x:c>
-      <x:c r="G9" s="12" t="str">
+      <x:c r="H9" s="12" t="str">
         <x:v>Pastèque</x:v>
       </x:c>
-      <x:c r="H9" s="12" t="str">
+      <x:c r="I9" s="12" t="str">
         <x:v>Sandía</x:v>
       </x:c>
-      <x:c r="I9" s="12" t="str">
+      <x:c r="J9" s="12" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="str">
+      <x:c r="K9" s="12" t="str">
         <x:v>Vandmelon er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -561,21 +571,24 @@
         <x:v>Citron</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
+        <x:v>Citron</x:v>
+      </x:c>
+      <x:c r="F10" s="12" t="str">
         <x:v>Lemon</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="str">
+      <x:c r="G10" s="12" t="str">
         <x:v>Zitrone</x:v>
       </x:c>
-      <x:c r="G10" s="12" t="str">
+      <x:c r="H10" s="12" t="str">
         <x:v>Citron</x:v>
       </x:c>
-      <x:c r="H10" s="12" t="str">
+      <x:c r="I10" s="12" t="str">
         <x:v>Limón</x:v>
       </x:c>
-      <x:c r="I10" s="12" t="str">
+      <x:c r="J10" s="12" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="str">
+      <x:c r="K10" s="12" t="str">
         <x:v>Citron er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -593,21 +606,24 @@
         <x:v>Fersken</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
+        <x:v>Fersken</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="str">
         <x:v>Peach</x:v>
       </x:c>
-      <x:c r="F11" s="12" t="str">
+      <x:c r="G11" s="12" t="str">
         <x:v>Pfirsich</x:v>
       </x:c>
-      <x:c r="G11" s="12" t="str">
+      <x:c r="H11" s="12" t="str">
         <x:v>Pêche</x:v>
       </x:c>
-      <x:c r="H11" s="12" t="str">
+      <x:c r="I11" s="12" t="str">
         <x:v>Melocotón</x:v>
       </x:c>
-      <x:c r="I11" s="12" t="str">
+      <x:c r="J11" s="12" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="str">
+      <x:c r="K11" s="12" t="str">
         <x:v>Fersken er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -625,21 +641,24 @@
         <x:v>Gulerod</x:v>
       </x:c>
       <x:c r="E12" s="12" t="str">
+        <x:v>Gulerod</x:v>
+      </x:c>
+      <x:c r="F12" s="12" t="str">
         <x:v>Carrot</x:v>
       </x:c>
-      <x:c r="F12" s="12" t="str">
+      <x:c r="G12" s="12" t="str">
         <x:v>Karotte</x:v>
       </x:c>
-      <x:c r="G12" s="12" t="str">
+      <x:c r="H12" s="12" t="str">
         <x:v>Carotte</x:v>
       </x:c>
-      <x:c r="H12" s="12" t="str">
+      <x:c r="I12" s="12" t="str">
         <x:v>Zanahoria</x:v>
       </x:c>
-      <x:c r="I12" s="12" t="str">
-        <x:v>Grøntsag</x:v>
-      </x:c>
       <x:c r="J12" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K12" s="12" t="str">
         <x:v>Gulerod er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -657,21 +676,24 @@
         <x:v>Kartoffel</x:v>
       </x:c>
       <x:c r="E13" s="12" t="str">
+        <x:v>Kartoffel</x:v>
+      </x:c>
+      <x:c r="F13" s="12" t="str">
         <x:v>Potato</x:v>
       </x:c>
-      <x:c r="F13" s="12" t="str">
+      <x:c r="G13" s="12" t="str">
         <x:v>Kartoffel</x:v>
       </x:c>
-      <x:c r="G13" s="12" t="str">
+      <x:c r="H13" s="12" t="str">
         <x:v>Pomme de terre</x:v>
       </x:c>
-      <x:c r="H13" s="12" t="str">
+      <x:c r="I13" s="12" t="str">
         <x:v>Patata</x:v>
       </x:c>
-      <x:c r="I13" s="12" t="str">
-        <x:v>Grøntsag</x:v>
-      </x:c>
       <x:c r="J13" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K13" s="12" t="str">
         <x:v>Kartoffel er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -689,10 +711,10 @@
         <x:v>Tomat</x:v>
       </x:c>
       <x:c r="E14" s="12" t="str">
+        <x:v>Tomat</x:v>
+      </x:c>
+      <x:c r="F14" s="12" t="str">
         <x:v>Tomato</x:v>
-      </x:c>
-      <x:c r="F14" s="12" t="str">
-        <x:v>Tomate</x:v>
       </x:c>
       <x:c r="G14" s="12" t="str">
         <x:v>Tomate</x:v>
@@ -701,9 +723,12 @@
         <x:v>Tomate</x:v>
       </x:c>
       <x:c r="I14" s="12" t="str">
-        <x:v>Grøntsag</x:v>
+        <x:v>Tomate</x:v>
       </x:c>
       <x:c r="J14" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K14" s="12" t="str">
         <x:v>Tomat er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -721,21 +746,24 @@
         <x:v>Agurk</x:v>
       </x:c>
       <x:c r="E15" s="12" t="str">
+        <x:v>Agurk</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="str">
         <x:v>Cucumber</x:v>
       </x:c>
-      <x:c r="F15" s="12" t="str">
+      <x:c r="G15" s="12" t="str">
         <x:v>Gurke</x:v>
       </x:c>
-      <x:c r="G15" s="12" t="str">
+      <x:c r="H15" s="12" t="str">
         <x:v>Concombre</x:v>
       </x:c>
-      <x:c r="H15" s="12" t="str">
+      <x:c r="I15" s="12" t="str">
         <x:v>Pepino</x:v>
       </x:c>
-      <x:c r="I15" s="12" t="str">
-        <x:v>Grøntsag</x:v>
-      </x:c>
       <x:c r="J15" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K15" s="12" t="str">
         <x:v>Agurk er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -756,18 +784,21 @@
         <x:v>Broccoli</x:v>
       </x:c>
       <x:c r="F16" s="12" t="str">
+        <x:v>Broccoli</x:v>
+      </x:c>
+      <x:c r="G16" s="12" t="str">
         <x:v>Brokkoli</x:v>
       </x:c>
-      <x:c r="G16" s="12" t="str">
+      <x:c r="H16" s="12" t="str">
         <x:v>Brocoli</x:v>
       </x:c>
-      <x:c r="H16" s="12" t="str">
+      <x:c r="I16" s="12" t="str">
         <x:v>Brócoli</x:v>
       </x:c>
-      <x:c r="I16" s="12" t="str">
-        <x:v>Grøntsag</x:v>
-      </x:c>
       <x:c r="J16" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K16" s="12" t="str">
         <x:v>Broccoli er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -785,21 +816,24 @@
         <x:v>Løg</x:v>
       </x:c>
       <x:c r="E17" s="12" t="str">
+        <x:v>Løg</x:v>
+      </x:c>
+      <x:c r="F17" s="12" t="str">
         <x:v>Onion</x:v>
       </x:c>
-      <x:c r="F17" s="12" t="str">
+      <x:c r="G17" s="12" t="str">
         <x:v>Zwiebel</x:v>
       </x:c>
-      <x:c r="G17" s="12" t="str">
+      <x:c r="H17" s="12" t="str">
         <x:v>Oignon</x:v>
       </x:c>
-      <x:c r="H17" s="12" t="str">
+      <x:c r="I17" s="12" t="str">
         <x:v>Cebolla</x:v>
       </x:c>
-      <x:c r="I17" s="12" t="str">
-        <x:v>Grøntsag</x:v>
-      </x:c>
       <x:c r="J17" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K17" s="12" t="str">
         <x:v>Løg er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -817,21 +851,24 @@
         <x:v>Peberfrugt</x:v>
       </x:c>
       <x:c r="E18" s="12" t="str">
+        <x:v>Peberfrugt</x:v>
+      </x:c>
+      <x:c r="F18" s="12" t="str">
         <x:v>Bell pepper</x:v>
       </x:c>
-      <x:c r="F18" s="12" t="str">
+      <x:c r="G18" s="12" t="str">
         <x:v>Paprika</x:v>
       </x:c>
-      <x:c r="G18" s="12" t="str">
+      <x:c r="H18" s="12" t="str">
         <x:v>Poivron</x:v>
       </x:c>
-      <x:c r="H18" s="12" t="str">
+      <x:c r="I18" s="12" t="str">
         <x:v>Pimiento</x:v>
       </x:c>
-      <x:c r="I18" s="12" t="str">
-        <x:v>Grøntsag</x:v>
-      </x:c>
       <x:c r="J18" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K18" s="12" t="str">
         <x:v>Peberfrugt er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -849,21 +886,24 @@
         <x:v>Majs</x:v>
       </x:c>
       <x:c r="E19" s="12" t="str">
+        <x:v>Majs</x:v>
+      </x:c>
+      <x:c r="F19" s="12" t="str">
         <x:v>Corn</x:v>
       </x:c>
-      <x:c r="F19" s="12" t="str">
+      <x:c r="G19" s="12" t="str">
         <x:v>Mais</x:v>
       </x:c>
-      <x:c r="G19" s="12" t="str">
+      <x:c r="H19" s="12" t="str">
         <x:v>Maïs</x:v>
       </x:c>
-      <x:c r="H19" s="12" t="str">
+      <x:c r="I19" s="12" t="str">
         <x:v>Maíz</x:v>
       </x:c>
-      <x:c r="I19" s="12" t="str">
-        <x:v>Grøntsag</x:v>
-      </x:c>
       <x:c r="J19" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K19" s="12" t="str">
         <x:v>Majs er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -881,21 +921,24 @@
         <x:v>Champignon</x:v>
       </x:c>
       <x:c r="E20" s="12" t="str">
+        <x:v>Champignon</x:v>
+      </x:c>
+      <x:c r="F20" s="12" t="str">
         <x:v>Mushroom</x:v>
       </x:c>
-      <x:c r="F20" s="12" t="str">
+      <x:c r="G20" s="12" t="str">
         <x:v>Pilz</x:v>
       </x:c>
-      <x:c r="G20" s="12" t="str">
+      <x:c r="H20" s="12" t="str">
         <x:v>Champignon</x:v>
       </x:c>
-      <x:c r="H20" s="12" t="str">
+      <x:c r="I20" s="12" t="str">
         <x:v>Champiñón</x:v>
       </x:c>
-      <x:c r="I20" s="12" t="str">
-        <x:v>Grøntsag</x:v>
-      </x:c>
       <x:c r="J20" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K20" s="12" t="str">
         <x:v>Champignon er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -913,21 +956,24 @@
         <x:v>Salat</x:v>
       </x:c>
       <x:c r="E21" s="12" t="str">
+        <x:v>Salat</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="str">
         <x:v>Lettuce</x:v>
       </x:c>
-      <x:c r="F21" s="12" t="str">
+      <x:c r="G21" s="12" t="str">
         <x:v>Salat</x:v>
       </x:c>
-      <x:c r="G21" s="12" t="str">
+      <x:c r="H21" s="12" t="str">
         <x:v>Laitue</x:v>
       </x:c>
-      <x:c r="H21" s="12" t="str">
+      <x:c r="I21" s="12" t="str">
         <x:v>Lechuga</x:v>
       </x:c>
-      <x:c r="I21" s="12" t="str">
-        <x:v>Grøntsag</x:v>
-      </x:c>
       <x:c r="J21" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K21" s="12" t="str">
         <x:v>Salat er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -957,9 +1003,12 @@
         <x:v>Kiwi</x:v>
       </x:c>
       <x:c r="I22" s="12" t="str">
+        <x:v>Kiwi</x:v>
+      </x:c>
+      <x:c r="J22" s="12" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="J22" s="12" t="str">
+      <x:c r="K22" s="12" t="str">
         <x:v>Kiwi er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -977,21 +1026,24 @@
         <x:v>Kirsebær</x:v>
       </x:c>
       <x:c r="E23" s="12" t="str">
+        <x:v>Kirsebær</x:v>
+      </x:c>
+      <x:c r="F23" s="12" t="str">
         <x:v>Cherry</x:v>
       </x:c>
-      <x:c r="F23" s="12" t="str">
+      <x:c r="G23" s="12" t="str">
         <x:v>Kirsche</x:v>
       </x:c>
-      <x:c r="G23" s="12" t="str">
+      <x:c r="H23" s="12" t="str">
         <x:v>Cerise</x:v>
       </x:c>
-      <x:c r="H23" s="12" t="str">
+      <x:c r="I23" s="12" t="str">
         <x:v>Cereza</x:v>
       </x:c>
-      <x:c r="I23" s="12" t="str">
+      <x:c r="J23" s="12" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="J23" s="12" t="str">
+      <x:c r="K23" s="12" t="str">
         <x:v>Kirsebær er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -1009,21 +1061,24 @@
         <x:v>Græskar</x:v>
       </x:c>
       <x:c r="E24" s="12" t="str">
+        <x:v>Græskar</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="str">
         <x:v>Pumpkin</x:v>
       </x:c>
-      <x:c r="F24" s="12" t="str">
+      <x:c r="G24" s="12" t="str">
         <x:v>Kürbis</x:v>
       </x:c>
-      <x:c r="G24" s="12" t="str">
+      <x:c r="H24" s="12" t="str">
         <x:v>Citrouille</x:v>
       </x:c>
-      <x:c r="H24" s="12" t="str">
+      <x:c r="I24" s="12" t="str">
         <x:v>Calabaza</x:v>
       </x:c>
-      <x:c r="I24" s="12" t="str">
-        <x:v>Grøntsag</x:v>
-      </x:c>
       <x:c r="J24" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K24" s="12" t="str">
         <x:v>Græskar er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -1041,21 +1096,24 @@
         <x:v>Aubergine</x:v>
       </x:c>
       <x:c r="E25" s="12" t="str">
+        <x:v>Aubergine</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="str">
         <x:v>Eggplant</x:v>
-      </x:c>
-      <x:c r="F25" s="12" t="str">
-        <x:v>Aubergine</x:v>
       </x:c>
       <x:c r="G25" s="12" t="str">
         <x:v>Aubergine</x:v>
       </x:c>
       <x:c r="H25" s="12" t="str">
+        <x:v>Aubergine</x:v>
+      </x:c>
+      <x:c r="I25" s="12" t="str">
         <x:v>Berenjena</x:v>
       </x:c>
-      <x:c r="I25" s="12" t="str">
-        <x:v>Grøntsag</x:v>
-      </x:c>
       <x:c r="J25" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K25" s="12" t="str">
         <x:v>Aubergine er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
@@ -1073,28 +1131,28 @@
         <x:v>Ærter</x:v>
       </x:c>
       <x:c r="E26" s="12" t="str">
+        <x:v>Ærter</x:v>
+      </x:c>
+      <x:c r="F26" s="12" t="str">
         <x:v>Peas</x:v>
       </x:c>
-      <x:c r="F26" s="12" t="str">
+      <x:c r="G26" s="12" t="str">
         <x:v>Erbsen</x:v>
       </x:c>
-      <x:c r="G26" s="12" t="str">
+      <x:c r="H26" s="12" t="str">
         <x:v>Petits pois</x:v>
       </x:c>
-      <x:c r="H26" s="12" t="str">
+      <x:c r="I26" s="12" t="str">
         <x:v>Guisantes</x:v>
       </x:c>
-      <x:c r="I26" s="12" t="str">
-        <x:v>Grøntsag</x:v>
-      </x:c>
       <x:c r="J26" s="12" t="str">
+        <x:v>Grøntsag</x:v>
+      </x:c>
+      <x:c r="K26" s="12" t="str">
         <x:v>Ærter er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fba3f980934463b"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
--- a/navneleg-demo/fruit-vegetables/frugt_groent_flersproget_demo.xlsx
+++ b/navneleg-demo/fruit-vegetables/frugt_groent_flersproget_demo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frugt og grønt" sheetId="1" r:id="R2fd7fd9e3c9344bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FrugtGroent" sheetId="1" r:id="R8fdf243fc6c144e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF2563EB"/>
+        <x:fgColor rgb="FF1D4ED8"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -45,30 +45,24 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -78,6 +72,26 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FrugtGroentTable" displayName="FrugtGroentTable" ref="A1:L26" headerRowCount="1">
+  <x:tableColumns count="12">
+    <x:tableColumn id="1" name="KortID"/>
+    <x:tableColumn id="2" name="Billedfil"/>
+    <x:tableColumn id="3" name="Billedsti"/>
+    <x:tableColumn id="4" name="Forside"/>
+    <x:tableColumn id="5" name="Dansk"/>
+    <x:tableColumn id="6" name="English"/>
+    <x:tableColumn id="7" name="Deutsch"/>
+    <x:tableColumn id="8" name="Français"/>
+    <x:tableColumn id="9" name="Español"/>
+    <x:tableColumn id="10" name="Kategori"/>
+    <x:tableColumn id="11" name="Hint"/>
+    <x:tableColumn id="12" name="Bagside"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -229,930 +243,1012 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="5" t="str">
         <x:v>KortID</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Billedfil</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Billedsti</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Forside</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Dansk</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>English</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>Deutsch</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>Français</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="I1" s="5" t="str">
         <x:v>Español</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="J1" s="5" t="str">
         <x:v>Kategori</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="K1" s="5" t="str">
         <x:v>Hint</x:v>
       </x:c>
+      <x:c r="L1" s="5" t="str">
+        <x:v>Bagside</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="10" t="str">
         <x:v>FV01</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="10" t="str">
         <x:v>01_apple.png</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/01_apple.png</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="10" t="str">
         <x:v>Æble</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="10" t="str">
         <x:v>Æble</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="10" t="str">
         <x:v>Apple</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="G2" s="10" t="str">
         <x:v>Apfel</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="H2" s="10" t="str">
         <x:v>Pomme</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="10" t="str">
         <x:v>Manzana</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="J2" s="10" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str">
+      <x:c r="K2" s="10" t="str">
         <x:v>Æble er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L2" s="10" t="str">
+        <x:v>Apple</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A3" s="10" t="str">
         <x:v>FV02</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B3" s="10" t="str">
         <x:v>02_orange.png</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C3" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/02_orange.png</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
+      <x:c r="D3" s="10" t="str">
         <x:v>Appelsin</x:v>
       </x:c>
-      <x:c r="E3" s="12" t="str">
+      <x:c r="E3" s="10" t="str">
         <x:v>Appelsin</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="str">
+      <x:c r="F3" s="10" t="str">
         <x:v>Orange</x:v>
       </x:c>
-      <x:c r="G3" s="12" t="str">
+      <x:c r="G3" s="10" t="str">
         <x:v>Orange</x:v>
       </x:c>
-      <x:c r="H3" s="12" t="str">
+      <x:c r="H3" s="10" t="str">
         <x:v>Orange</x:v>
       </x:c>
-      <x:c r="I3" s="12" t="str">
+      <x:c r="I3" s="10" t="str">
         <x:v>Naranja</x:v>
       </x:c>
-      <x:c r="J3" s="12" t="str">
+      <x:c r="J3" s="10" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="K3" s="12" t="str">
+      <x:c r="K3" s="10" t="str">
         <x:v>Appelsin er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L3" s="10" t="str">
+        <x:v>Orange</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="12" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>FV03</x:v>
       </x:c>
-      <x:c r="B4" s="12" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>03_banana.png</x:v>
       </x:c>
-      <x:c r="C4" s="12" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/03_banana.png</x:v>
       </x:c>
-      <x:c r="D4" s="12" t="str">
+      <x:c r="D4" s="10" t="str">
         <x:v>Banan</x:v>
       </x:c>
-      <x:c r="E4" s="12" t="str">
+      <x:c r="E4" s="10" t="str">
         <x:v>Banan</x:v>
       </x:c>
-      <x:c r="F4" s="12" t="str">
+      <x:c r="F4" s="10" t="str">
         <x:v>Banana</x:v>
       </x:c>
-      <x:c r="G4" s="12" t="str">
+      <x:c r="G4" s="10" t="str">
         <x:v>Banane</x:v>
       </x:c>
-      <x:c r="H4" s="12" t="str">
+      <x:c r="H4" s="10" t="str">
         <x:v>Banane</x:v>
       </x:c>
-      <x:c r="I4" s="12" t="str">
+      <x:c r="I4" s="10" t="str">
         <x:v>Plátano</x:v>
       </x:c>
-      <x:c r="J4" s="12" t="str">
+      <x:c r="J4" s="10" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="K4" s="12" t="str">
+      <x:c r="K4" s="10" t="str">
         <x:v>Banan er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L4" s="10" t="str">
+        <x:v>Banana</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="12" t="str">
+      <x:c r="A5" s="10" t="str">
         <x:v>FV04</x:v>
       </x:c>
-      <x:c r="B5" s="12" t="str">
+      <x:c r="B5" s="10" t="str">
         <x:v>04_strawberry.png</x:v>
       </x:c>
-      <x:c r="C5" s="12" t="str">
+      <x:c r="C5" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/04_strawberry.png</x:v>
       </x:c>
-      <x:c r="D5" s="12" t="str">
+      <x:c r="D5" s="10" t="str">
         <x:v>Jordbær</x:v>
       </x:c>
-      <x:c r="E5" s="12" t="str">
+      <x:c r="E5" s="10" t="str">
         <x:v>Jordbær</x:v>
       </x:c>
-      <x:c r="F5" s="12" t="str">
+      <x:c r="F5" s="10" t="str">
         <x:v>Strawberry</x:v>
       </x:c>
-      <x:c r="G5" s="12" t="str">
+      <x:c r="G5" s="10" t="str">
         <x:v>Erdbeere</x:v>
       </x:c>
-      <x:c r="H5" s="12" t="str">
+      <x:c r="H5" s="10" t="str">
         <x:v>Fraise</x:v>
       </x:c>
-      <x:c r="I5" s="12" t="str">
+      <x:c r="I5" s="10" t="str">
         <x:v>Fresa</x:v>
       </x:c>
-      <x:c r="J5" s="12" t="str">
+      <x:c r="J5" s="10" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="K5" s="12" t="str">
+      <x:c r="K5" s="10" t="str">
         <x:v>Jordbær er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L5" s="10" t="str">
+        <x:v>Strawberry</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="12" t="str">
+      <x:c r="A6" s="10" t="str">
         <x:v>FV05</x:v>
       </x:c>
-      <x:c r="B6" s="12" t="str">
+      <x:c r="B6" s="10" t="str">
         <x:v>05_pear.png</x:v>
       </x:c>
-      <x:c r="C6" s="12" t="str">
+      <x:c r="C6" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/05_pear.png</x:v>
       </x:c>
-      <x:c r="D6" s="12" t="str">
+      <x:c r="D6" s="10" t="str">
         <x:v>Pære</x:v>
       </x:c>
-      <x:c r="E6" s="12" t="str">
+      <x:c r="E6" s="10" t="str">
         <x:v>Pære</x:v>
       </x:c>
-      <x:c r="F6" s="12" t="str">
+      <x:c r="F6" s="10" t="str">
         <x:v>Pear</x:v>
       </x:c>
-      <x:c r="G6" s="12" t="str">
+      <x:c r="G6" s="10" t="str">
         <x:v>Birne</x:v>
       </x:c>
-      <x:c r="H6" s="12" t="str">
+      <x:c r="H6" s="10" t="str">
         <x:v>Poire</x:v>
       </x:c>
-      <x:c r="I6" s="12" t="str">
+      <x:c r="I6" s="10" t="str">
         <x:v>Pera</x:v>
       </x:c>
-      <x:c r="J6" s="12" t="str">
+      <x:c r="J6" s="10" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="K6" s="12" t="str">
+      <x:c r="K6" s="10" t="str">
         <x:v>Pære er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L6" s="10" t="str">
+        <x:v>Pear</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="12" t="str">
+      <x:c r="A7" s="10" t="str">
         <x:v>FV06</x:v>
       </x:c>
-      <x:c r="B7" s="12" t="str">
+      <x:c r="B7" s="10" t="str">
         <x:v>06_grapes.png</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="str">
+      <x:c r="C7" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/06_grapes.png</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="str">
+      <x:c r="D7" s="10" t="str">
         <x:v>Vindruer</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="str">
+      <x:c r="E7" s="10" t="str">
         <x:v>Vindruer</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="str">
+      <x:c r="F7" s="10" t="str">
         <x:v>Grapes</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="str">
+      <x:c r="G7" s="10" t="str">
         <x:v>Trauben</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="str">
+      <x:c r="H7" s="10" t="str">
         <x:v>Raisins</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="str">
+      <x:c r="I7" s="10" t="str">
         <x:v>Uvas</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="str">
+      <x:c r="J7" s="10" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="str">
+      <x:c r="K7" s="10" t="str">
         <x:v>Vindruer er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L7" s="10" t="str">
+        <x:v>Grapes</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="12" t="str">
+      <x:c r="A8" s="10" t="str">
         <x:v>FV07</x:v>
       </x:c>
-      <x:c r="B8" s="12" t="str">
+      <x:c r="B8" s="10" t="str">
         <x:v>07_pineapple.png</x:v>
       </x:c>
-      <x:c r="C8" s="12" t="str">
+      <x:c r="C8" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/07_pineapple.png</x:v>
       </x:c>
-      <x:c r="D8" s="12" t="str">
+      <x:c r="D8" s="10" t="str">
         <x:v>Ananas</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="str">
+      <x:c r="E8" s="10" t="str">
         <x:v>Ananas</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="str">
+      <x:c r="F8" s="10" t="str">
         <x:v>Pineapple</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="str">
+      <x:c r="G8" s="10" t="str">
         <x:v>Ananas</x:v>
       </x:c>
-      <x:c r="H8" s="12" t="str">
+      <x:c r="H8" s="10" t="str">
         <x:v>Ananas</x:v>
       </x:c>
-      <x:c r="I8" s="12" t="str">
+      <x:c r="I8" s="10" t="str">
         <x:v>Piña</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="str">
+      <x:c r="J8" s="10" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="K8" s="12" t="str">
+      <x:c r="K8" s="10" t="str">
         <x:v>Ananas er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L8" s="10" t="str">
+        <x:v>Pineapple</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="12" t="str">
+      <x:c r="A9" s="10" t="str">
         <x:v>FV08</x:v>
       </x:c>
-      <x:c r="B9" s="12" t="str">
+      <x:c r="B9" s="10" t="str">
         <x:v>08_watermelon.png</x:v>
       </x:c>
-      <x:c r="C9" s="12" t="str">
+      <x:c r="C9" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/08_watermelon.png</x:v>
       </x:c>
-      <x:c r="D9" s="12" t="str">
+      <x:c r="D9" s="10" t="str">
         <x:v>Vandmelon</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="str">
+      <x:c r="E9" s="10" t="str">
         <x:v>Vandmelon</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="str">
+      <x:c r="F9" s="10" t="str">
         <x:v>Watermelon</x:v>
       </x:c>
-      <x:c r="G9" s="12" t="str">
+      <x:c r="G9" s="10" t="str">
         <x:v>Wassermelone</x:v>
       </x:c>
-      <x:c r="H9" s="12" t="str">
+      <x:c r="H9" s="10" t="str">
         <x:v>Pastèque</x:v>
       </x:c>
-      <x:c r="I9" s="12" t="str">
+      <x:c r="I9" s="10" t="str">
         <x:v>Sandía</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="str">
+      <x:c r="J9" s="10" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="K9" s="12" t="str">
+      <x:c r="K9" s="10" t="str">
         <x:v>Vandmelon er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L9" s="10" t="str">
+        <x:v>Watermelon</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="12" t="str">
+      <x:c r="A10" s="10" t="str">
         <x:v>FV09</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="str">
+      <x:c r="B10" s="10" t="str">
         <x:v>09_lemon.png</x:v>
       </x:c>
-      <x:c r="C10" s="12" t="str">
+      <x:c r="C10" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/09_lemon.png</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="str">
+      <x:c r="D10" s="10" t="str">
         <x:v>Citron</x:v>
       </x:c>
-      <x:c r="E10" s="12" t="str">
+      <x:c r="E10" s="10" t="str">
         <x:v>Citron</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="str">
+      <x:c r="F10" s="10" t="str">
         <x:v>Lemon</x:v>
       </x:c>
-      <x:c r="G10" s="12" t="str">
+      <x:c r="G10" s="10" t="str">
         <x:v>Zitrone</x:v>
       </x:c>
-      <x:c r="H10" s="12" t="str">
+      <x:c r="H10" s="10" t="str">
         <x:v>Citron</x:v>
       </x:c>
-      <x:c r="I10" s="12" t="str">
+      <x:c r="I10" s="10" t="str">
         <x:v>Limón</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="str">
+      <x:c r="J10" s="10" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="K10" s="12" t="str">
+      <x:c r="K10" s="10" t="str">
         <x:v>Citron er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L10" s="10" t="str">
+        <x:v>Lemon</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="12" t="str">
+      <x:c r="A11" s="10" t="str">
         <x:v>FV10</x:v>
       </x:c>
-      <x:c r="B11" s="12" t="str">
+      <x:c r="B11" s="10" t="str">
         <x:v>10_peach.png</x:v>
       </x:c>
-      <x:c r="C11" s="12" t="str">
+      <x:c r="C11" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/10_peach.png</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="str">
+      <x:c r="D11" s="10" t="str">
         <x:v>Fersken</x:v>
       </x:c>
-      <x:c r="E11" s="12" t="str">
+      <x:c r="E11" s="10" t="str">
         <x:v>Fersken</x:v>
       </x:c>
-      <x:c r="F11" s="12" t="str">
+      <x:c r="F11" s="10" t="str">
         <x:v>Peach</x:v>
       </x:c>
-      <x:c r="G11" s="12" t="str">
+      <x:c r="G11" s="10" t="str">
         <x:v>Pfirsich</x:v>
       </x:c>
-      <x:c r="H11" s="12" t="str">
+      <x:c r="H11" s="10" t="str">
         <x:v>Pêche</x:v>
       </x:c>
-      <x:c r="I11" s="12" t="str">
+      <x:c r="I11" s="10" t="str">
         <x:v>Melocotón</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="str">
+      <x:c r="J11" s="10" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="K11" s="12" t="str">
+      <x:c r="K11" s="10" t="str">
         <x:v>Fersken er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L11" s="10" t="str">
+        <x:v>Peach</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="12" t="str">
+      <x:c r="A12" s="10" t="str">
         <x:v>FV11</x:v>
       </x:c>
-      <x:c r="B12" s="12" t="str">
+      <x:c r="B12" s="10" t="str">
         <x:v>11_carrot.png</x:v>
       </x:c>
-      <x:c r="C12" s="12" t="str">
+      <x:c r="C12" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/11_carrot.png</x:v>
       </x:c>
-      <x:c r="D12" s="12" t="str">
+      <x:c r="D12" s="10" t="str">
         <x:v>Gulerod</x:v>
       </x:c>
-      <x:c r="E12" s="12" t="str">
+      <x:c r="E12" s="10" t="str">
         <x:v>Gulerod</x:v>
       </x:c>
-      <x:c r="F12" s="12" t="str">
+      <x:c r="F12" s="10" t="str">
         <x:v>Carrot</x:v>
       </x:c>
-      <x:c r="G12" s="12" t="str">
+      <x:c r="G12" s="10" t="str">
         <x:v>Karotte</x:v>
       </x:c>
-      <x:c r="H12" s="12" t="str">
+      <x:c r="H12" s="10" t="str">
         <x:v>Carotte</x:v>
       </x:c>
-      <x:c r="I12" s="12" t="str">
+      <x:c r="I12" s="10" t="str">
         <x:v>Zanahoria</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="str">
+      <x:c r="J12" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K12" s="12" t="str">
+      <x:c r="K12" s="10" t="str">
         <x:v>Gulerod er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L12" s="10" t="str">
+        <x:v>Carrot</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="12" t="str">
+      <x:c r="A13" s="10" t="str">
         <x:v>FV12</x:v>
       </x:c>
-      <x:c r="B13" s="12" t="str">
+      <x:c r="B13" s="10" t="str">
         <x:v>12_potato.png</x:v>
       </x:c>
-      <x:c r="C13" s="12" t="str">
+      <x:c r="C13" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/12_potato.png</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="str">
+      <x:c r="D13" s="10" t="str">
         <x:v>Kartoffel</x:v>
       </x:c>
-      <x:c r="E13" s="12" t="str">
+      <x:c r="E13" s="10" t="str">
         <x:v>Kartoffel</x:v>
       </x:c>
-      <x:c r="F13" s="12" t="str">
+      <x:c r="F13" s="10" t="str">
         <x:v>Potato</x:v>
       </x:c>
-      <x:c r="G13" s="12" t="str">
+      <x:c r="G13" s="10" t="str">
         <x:v>Kartoffel</x:v>
       </x:c>
-      <x:c r="H13" s="12" t="str">
+      <x:c r="H13" s="10" t="str">
         <x:v>Pomme de terre</x:v>
       </x:c>
-      <x:c r="I13" s="12" t="str">
+      <x:c r="I13" s="10" t="str">
         <x:v>Patata</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="str">
+      <x:c r="J13" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K13" s="12" t="str">
+      <x:c r="K13" s="10" t="str">
         <x:v>Kartoffel er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L13" s="10" t="str">
+        <x:v>Potato</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="12" t="str">
+      <x:c r="A14" s="10" t="str">
         <x:v>FV13</x:v>
       </x:c>
-      <x:c r="B14" s="12" t="str">
+      <x:c r="B14" s="10" t="str">
         <x:v>13_tomato.png</x:v>
       </x:c>
-      <x:c r="C14" s="12" t="str">
+      <x:c r="C14" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/13_tomato.png</x:v>
       </x:c>
-      <x:c r="D14" s="12" t="str">
+      <x:c r="D14" s="10" t="str">
         <x:v>Tomat</x:v>
       </x:c>
-      <x:c r="E14" s="12" t="str">
+      <x:c r="E14" s="10" t="str">
         <x:v>Tomat</x:v>
       </x:c>
-      <x:c r="F14" s="12" t="str">
+      <x:c r="F14" s="10" t="str">
         <x:v>Tomato</x:v>
       </x:c>
-      <x:c r="G14" s="12" t="str">
+      <x:c r="G14" s="10" t="str">
         <x:v>Tomate</x:v>
       </x:c>
-      <x:c r="H14" s="12" t="str">
+      <x:c r="H14" s="10" t="str">
         <x:v>Tomate</x:v>
       </x:c>
-      <x:c r="I14" s="12" t="str">
+      <x:c r="I14" s="10" t="str">
         <x:v>Tomate</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="str">
+      <x:c r="J14" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K14" s="12" t="str">
+      <x:c r="K14" s="10" t="str">
         <x:v>Tomat er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L14" s="10" t="str">
+        <x:v>Tomato</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="12" t="str">
+      <x:c r="A15" s="10" t="str">
         <x:v>FV14</x:v>
       </x:c>
-      <x:c r="B15" s="12" t="str">
+      <x:c r="B15" s="10" t="str">
         <x:v>14_cucumber.png</x:v>
       </x:c>
-      <x:c r="C15" s="12" t="str">
+      <x:c r="C15" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/14_cucumber.png</x:v>
       </x:c>
-      <x:c r="D15" s="12" t="str">
+      <x:c r="D15" s="10" t="str">
         <x:v>Agurk</x:v>
       </x:c>
-      <x:c r="E15" s="12" t="str">
+      <x:c r="E15" s="10" t="str">
         <x:v>Agurk</x:v>
       </x:c>
-      <x:c r="F15" s="12" t="str">
+      <x:c r="F15" s="10" t="str">
         <x:v>Cucumber</x:v>
       </x:c>
-      <x:c r="G15" s="12" t="str">
+      <x:c r="G15" s="10" t="str">
         <x:v>Gurke</x:v>
       </x:c>
-      <x:c r="H15" s="12" t="str">
+      <x:c r="H15" s="10" t="str">
         <x:v>Concombre</x:v>
       </x:c>
-      <x:c r="I15" s="12" t="str">
+      <x:c r="I15" s="10" t="str">
         <x:v>Pepino</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="str">
+      <x:c r="J15" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K15" s="12" t="str">
+      <x:c r="K15" s="10" t="str">
         <x:v>Agurk er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L15" s="10" t="str">
+        <x:v>Cucumber</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="12" t="str">
+      <x:c r="A16" s="10" t="str">
         <x:v>FV15</x:v>
       </x:c>
-      <x:c r="B16" s="12" t="str">
+      <x:c r="B16" s="10" t="str">
         <x:v>15_broccoli.png</x:v>
       </x:c>
-      <x:c r="C16" s="12" t="str">
+      <x:c r="C16" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/15_broccoli.png</x:v>
       </x:c>
-      <x:c r="D16" s="12" t="str">
+      <x:c r="D16" s="10" t="str">
         <x:v>Broccoli</x:v>
       </x:c>
-      <x:c r="E16" s="12" t="str">
+      <x:c r="E16" s="10" t="str">
         <x:v>Broccoli</x:v>
       </x:c>
-      <x:c r="F16" s="12" t="str">
+      <x:c r="F16" s="10" t="str">
         <x:v>Broccoli</x:v>
       </x:c>
-      <x:c r="G16" s="12" t="str">
+      <x:c r="G16" s="10" t="str">
         <x:v>Brokkoli</x:v>
       </x:c>
-      <x:c r="H16" s="12" t="str">
+      <x:c r="H16" s="10" t="str">
         <x:v>Brocoli</x:v>
       </x:c>
-      <x:c r="I16" s="12" t="str">
+      <x:c r="I16" s="10" t="str">
         <x:v>Brócoli</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="str">
+      <x:c r="J16" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K16" s="12" t="str">
+      <x:c r="K16" s="10" t="str">
         <x:v>Broccoli er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L16" s="10" t="str">
+        <x:v>Broccoli</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="12" t="str">
+      <x:c r="A17" s="10" t="str">
         <x:v>FV16</x:v>
       </x:c>
-      <x:c r="B17" s="12" t="str">
+      <x:c r="B17" s="10" t="str">
         <x:v>16_onion.png</x:v>
       </x:c>
-      <x:c r="C17" s="12" t="str">
+      <x:c r="C17" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/16_onion.png</x:v>
       </x:c>
-      <x:c r="D17" s="12" t="str">
+      <x:c r="D17" s="10" t="str">
         <x:v>Løg</x:v>
       </x:c>
-      <x:c r="E17" s="12" t="str">
+      <x:c r="E17" s="10" t="str">
         <x:v>Løg</x:v>
       </x:c>
-      <x:c r="F17" s="12" t="str">
+      <x:c r="F17" s="10" t="str">
         <x:v>Onion</x:v>
       </x:c>
-      <x:c r="G17" s="12" t="str">
+      <x:c r="G17" s="10" t="str">
         <x:v>Zwiebel</x:v>
       </x:c>
-      <x:c r="H17" s="12" t="str">
+      <x:c r="H17" s="10" t="str">
         <x:v>Oignon</x:v>
       </x:c>
-      <x:c r="I17" s="12" t="str">
+      <x:c r="I17" s="10" t="str">
         <x:v>Cebolla</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="str">
+      <x:c r="J17" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K17" s="12" t="str">
+      <x:c r="K17" s="10" t="str">
         <x:v>Løg er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L17" s="10" t="str">
+        <x:v>Onion</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="12" t="str">
+      <x:c r="A18" s="10" t="str">
         <x:v>FV17</x:v>
       </x:c>
-      <x:c r="B18" s="12" t="str">
+      <x:c r="B18" s="10" t="str">
         <x:v>17_pepper.png</x:v>
       </x:c>
-      <x:c r="C18" s="12" t="str">
+      <x:c r="C18" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/17_pepper.png</x:v>
       </x:c>
-      <x:c r="D18" s="12" t="str">
+      <x:c r="D18" s="10" t="str">
         <x:v>Peberfrugt</x:v>
       </x:c>
-      <x:c r="E18" s="12" t="str">
+      <x:c r="E18" s="10" t="str">
         <x:v>Peberfrugt</x:v>
       </x:c>
-      <x:c r="F18" s="12" t="str">
+      <x:c r="F18" s="10" t="str">
         <x:v>Bell pepper</x:v>
       </x:c>
-      <x:c r="G18" s="12" t="str">
+      <x:c r="G18" s="10" t="str">
         <x:v>Paprika</x:v>
       </x:c>
-      <x:c r="H18" s="12" t="str">
+      <x:c r="H18" s="10" t="str">
         <x:v>Poivron</x:v>
       </x:c>
-      <x:c r="I18" s="12" t="str">
+      <x:c r="I18" s="10" t="str">
         <x:v>Pimiento</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="str">
+      <x:c r="J18" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K18" s="12" t="str">
+      <x:c r="K18" s="10" t="str">
         <x:v>Peberfrugt er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L18" s="10" t="str">
+        <x:v>Bell pepper</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="12" t="str">
+      <x:c r="A19" s="10" t="str">
         <x:v>FV18</x:v>
       </x:c>
-      <x:c r="B19" s="12" t="str">
+      <x:c r="B19" s="10" t="str">
         <x:v>18_corn.png</x:v>
       </x:c>
-      <x:c r="C19" s="12" t="str">
+      <x:c r="C19" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/18_corn.png</x:v>
       </x:c>
-      <x:c r="D19" s="12" t="str">
+      <x:c r="D19" s="10" t="str">
         <x:v>Majs</x:v>
       </x:c>
-      <x:c r="E19" s="12" t="str">
+      <x:c r="E19" s="10" t="str">
         <x:v>Majs</x:v>
       </x:c>
-      <x:c r="F19" s="12" t="str">
+      <x:c r="F19" s="10" t="str">
         <x:v>Corn</x:v>
       </x:c>
-      <x:c r="G19" s="12" t="str">
+      <x:c r="G19" s="10" t="str">
         <x:v>Mais</x:v>
       </x:c>
-      <x:c r="H19" s="12" t="str">
+      <x:c r="H19" s="10" t="str">
         <x:v>Maïs</x:v>
       </x:c>
-      <x:c r="I19" s="12" t="str">
+      <x:c r="I19" s="10" t="str">
         <x:v>Maíz</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="str">
+      <x:c r="J19" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K19" s="12" t="str">
+      <x:c r="K19" s="10" t="str">
         <x:v>Majs er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L19" s="10" t="str">
+        <x:v>Corn</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="12" t="str">
+      <x:c r="A20" s="10" t="str">
         <x:v>FV19</x:v>
       </x:c>
-      <x:c r="B20" s="12" t="str">
+      <x:c r="B20" s="10" t="str">
         <x:v>19_mushroom.png</x:v>
       </x:c>
-      <x:c r="C20" s="12" t="str">
+      <x:c r="C20" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/19_mushroom.png</x:v>
       </x:c>
-      <x:c r="D20" s="12" t="str">
+      <x:c r="D20" s="10" t="str">
         <x:v>Champignon</x:v>
       </x:c>
-      <x:c r="E20" s="12" t="str">
+      <x:c r="E20" s="10" t="str">
         <x:v>Champignon</x:v>
       </x:c>
-      <x:c r="F20" s="12" t="str">
+      <x:c r="F20" s="10" t="str">
         <x:v>Mushroom</x:v>
       </x:c>
-      <x:c r="G20" s="12" t="str">
+      <x:c r="G20" s="10" t="str">
         <x:v>Pilz</x:v>
       </x:c>
-      <x:c r="H20" s="12" t="str">
+      <x:c r="H20" s="10" t="str">
         <x:v>Champignon</x:v>
       </x:c>
-      <x:c r="I20" s="12" t="str">
+      <x:c r="I20" s="10" t="str">
         <x:v>Champiñón</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="str">
+      <x:c r="J20" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K20" s="12" t="str">
+      <x:c r="K20" s="10" t="str">
         <x:v>Champignon er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L20" s="10" t="str">
+        <x:v>Mushroom</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="12" t="str">
+      <x:c r="A21" s="10" t="str">
         <x:v>FV20</x:v>
       </x:c>
-      <x:c r="B21" s="12" t="str">
+      <x:c r="B21" s="10" t="str">
         <x:v>20_lettuce.png</x:v>
       </x:c>
-      <x:c r="C21" s="12" t="str">
+      <x:c r="C21" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/20_lettuce.png</x:v>
       </x:c>
-      <x:c r="D21" s="12" t="str">
+      <x:c r="D21" s="10" t="str">
         <x:v>Salat</x:v>
       </x:c>
-      <x:c r="E21" s="12" t="str">
+      <x:c r="E21" s="10" t="str">
         <x:v>Salat</x:v>
       </x:c>
-      <x:c r="F21" s="12" t="str">
+      <x:c r="F21" s="10" t="str">
         <x:v>Lettuce</x:v>
       </x:c>
-      <x:c r="G21" s="12" t="str">
+      <x:c r="G21" s="10" t="str">
         <x:v>Salat</x:v>
       </x:c>
-      <x:c r="H21" s="12" t="str">
+      <x:c r="H21" s="10" t="str">
         <x:v>Laitue</x:v>
       </x:c>
-      <x:c r="I21" s="12" t="str">
+      <x:c r="I21" s="10" t="str">
         <x:v>Lechuga</x:v>
       </x:c>
-      <x:c r="J21" s="12" t="str">
+      <x:c r="J21" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K21" s="12" t="str">
+      <x:c r="K21" s="10" t="str">
         <x:v>Salat er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L21" s="10" t="str">
+        <x:v>Lettuce</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="12" t="str">
+      <x:c r="A22" s="10" t="str">
         <x:v>FV21</x:v>
       </x:c>
-      <x:c r="B22" s="12" t="str">
+      <x:c r="B22" s="10" t="str">
         <x:v>21_kiwi.png</x:v>
       </x:c>
-      <x:c r="C22" s="12" t="str">
+      <x:c r="C22" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/21_kiwi.png</x:v>
       </x:c>
-      <x:c r="D22" s="12" t="str">
+      <x:c r="D22" s="10" t="str">
         <x:v>Kiwi</x:v>
       </x:c>
-      <x:c r="E22" s="12" t="str">
+      <x:c r="E22" s="10" t="str">
         <x:v>Kiwi</x:v>
       </x:c>
-      <x:c r="F22" s="12" t="str">
+      <x:c r="F22" s="10" t="str">
         <x:v>Kiwi</x:v>
       </x:c>
-      <x:c r="G22" s="12" t="str">
+      <x:c r="G22" s="10" t="str">
         <x:v>Kiwi</x:v>
       </x:c>
-      <x:c r="H22" s="12" t="str">
+      <x:c r="H22" s="10" t="str">
         <x:v>Kiwi</x:v>
       </x:c>
-      <x:c r="I22" s="12" t="str">
+      <x:c r="I22" s="10" t="str">
         <x:v>Kiwi</x:v>
       </x:c>
-      <x:c r="J22" s="12" t="str">
+      <x:c r="J22" s="10" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="K22" s="12" t="str">
+      <x:c r="K22" s="10" t="str">
         <x:v>Kiwi er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L22" s="10" t="str">
+        <x:v>Kiwi</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="12" t="str">
+      <x:c r="A23" s="10" t="str">
         <x:v>FV22</x:v>
       </x:c>
-      <x:c r="B23" s="12" t="str">
+      <x:c r="B23" s="10" t="str">
         <x:v>22_cherry.png</x:v>
       </x:c>
-      <x:c r="C23" s="12" t="str">
+      <x:c r="C23" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/22_cherry.png</x:v>
       </x:c>
-      <x:c r="D23" s="12" t="str">
+      <x:c r="D23" s="10" t="str">
         <x:v>Kirsebær</x:v>
       </x:c>
-      <x:c r="E23" s="12" t="str">
+      <x:c r="E23" s="10" t="str">
         <x:v>Kirsebær</x:v>
       </x:c>
-      <x:c r="F23" s="12" t="str">
+      <x:c r="F23" s="10" t="str">
         <x:v>Cherry</x:v>
       </x:c>
-      <x:c r="G23" s="12" t="str">
+      <x:c r="G23" s="10" t="str">
         <x:v>Kirsche</x:v>
       </x:c>
-      <x:c r="H23" s="12" t="str">
+      <x:c r="H23" s="10" t="str">
         <x:v>Cerise</x:v>
       </x:c>
-      <x:c r="I23" s="12" t="str">
+      <x:c r="I23" s="10" t="str">
         <x:v>Cereza</x:v>
       </x:c>
-      <x:c r="J23" s="12" t="str">
+      <x:c r="J23" s="10" t="str">
         <x:v>Frugt</x:v>
       </x:c>
-      <x:c r="K23" s="12" t="str">
+      <x:c r="K23" s="10" t="str">
         <x:v>Kirsebær er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L23" s="10" t="str">
+        <x:v>Cherry</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="12" t="str">
+      <x:c r="A24" s="10" t="str">
         <x:v>FV23</x:v>
       </x:c>
-      <x:c r="B24" s="12" t="str">
+      <x:c r="B24" s="10" t="str">
         <x:v>23_pumpkin.png</x:v>
       </x:c>
-      <x:c r="C24" s="12" t="str">
+      <x:c r="C24" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/23_pumpkin.png</x:v>
       </x:c>
-      <x:c r="D24" s="12" t="str">
+      <x:c r="D24" s="10" t="str">
         <x:v>Græskar</x:v>
       </x:c>
-      <x:c r="E24" s="12" t="str">
+      <x:c r="E24" s="10" t="str">
         <x:v>Græskar</x:v>
       </x:c>
-      <x:c r="F24" s="12" t="str">
+      <x:c r="F24" s="10" t="str">
         <x:v>Pumpkin</x:v>
       </x:c>
-      <x:c r="G24" s="12" t="str">
+      <x:c r="G24" s="10" t="str">
         <x:v>Kürbis</x:v>
       </x:c>
-      <x:c r="H24" s="12" t="str">
+      <x:c r="H24" s="10" t="str">
         <x:v>Citrouille</x:v>
       </x:c>
-      <x:c r="I24" s="12" t="str">
+      <x:c r="I24" s="10" t="str">
         <x:v>Calabaza</x:v>
       </x:c>
-      <x:c r="J24" s="12" t="str">
+      <x:c r="J24" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K24" s="12" t="str">
+      <x:c r="K24" s="10" t="str">
         <x:v>Græskar er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L24" s="10" t="str">
+        <x:v>Pumpkin</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="12" t="str">
+      <x:c r="A25" s="10" t="str">
         <x:v>FV24</x:v>
       </x:c>
-      <x:c r="B25" s="12" t="str">
+      <x:c r="B25" s="10" t="str">
         <x:v>24_eggplant.png</x:v>
       </x:c>
-      <x:c r="C25" s="12" t="str">
+      <x:c r="C25" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/24_eggplant.png</x:v>
       </x:c>
-      <x:c r="D25" s="12" t="str">
+      <x:c r="D25" s="10" t="str">
         <x:v>Aubergine</x:v>
       </x:c>
-      <x:c r="E25" s="12" t="str">
+      <x:c r="E25" s="10" t="str">
         <x:v>Aubergine</x:v>
       </x:c>
-      <x:c r="F25" s="12" t="str">
+      <x:c r="F25" s="10" t="str">
         <x:v>Eggplant</x:v>
       </x:c>
-      <x:c r="G25" s="12" t="str">
+      <x:c r="G25" s="10" t="str">
         <x:v>Aubergine</x:v>
       </x:c>
-      <x:c r="H25" s="12" t="str">
+      <x:c r="H25" s="10" t="str">
         <x:v>Aubergine</x:v>
       </x:c>
-      <x:c r="I25" s="12" t="str">
+      <x:c r="I25" s="10" t="str">
         <x:v>Berenjena</x:v>
       </x:c>
-      <x:c r="J25" s="12" t="str">
+      <x:c r="J25" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K25" s="12" t="str">
+      <x:c r="K25" s="10" t="str">
         <x:v>Aubergine er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
       </x:c>
+      <x:c r="L25" s="10" t="str">
+        <x:v>Eggplant</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="12" t="str">
+      <x:c r="A26" s="10" t="str">
         <x:v>FV25</x:v>
       </x:c>
-      <x:c r="B26" s="12" t="str">
+      <x:c r="B26" s="10" t="str">
         <x:v>25_peas.png</x:v>
       </x:c>
-      <x:c r="C26" s="12" t="str">
+      <x:c r="C26" s="10" t="str">
         <x:v>navneleg-demo/fruit-vegetables/photos/25_peas.png</x:v>
       </x:c>
-      <x:c r="D26" s="12" t="str">
+      <x:c r="D26" s="10" t="str">
         <x:v>Ærter</x:v>
       </x:c>
-      <x:c r="E26" s="12" t="str">
+      <x:c r="E26" s="10" t="str">
         <x:v>Ærter</x:v>
       </x:c>
-      <x:c r="F26" s="12" t="str">
+      <x:c r="F26" s="10" t="str">
         <x:v>Peas</x:v>
       </x:c>
-      <x:c r="G26" s="12" t="str">
+      <x:c r="G26" s="10" t="str">
         <x:v>Erbsen</x:v>
       </x:c>
-      <x:c r="H26" s="12" t="str">
+      <x:c r="H26" s="10" t="str">
         <x:v>Petits pois</x:v>
       </x:c>
-      <x:c r="I26" s="12" t="str">
+      <x:c r="I26" s="10" t="str">
         <x:v>Guisantes</x:v>
       </x:c>
-      <x:c r="J26" s="12" t="str">
+      <x:c r="J26" s="10" t="str">
         <x:v>Grøntsag</x:v>
       </x:c>
-      <x:c r="K26" s="12" t="str">
+      <x:c r="K26" s="10" t="str">
         <x:v>Ærter er tydelig på billedet — men bagsiden kan være engelsk, tysk, fransk eller spansk.</x:v>
+      </x:c>
+      <x:c r="L26" s="10" t="str">
+        <x:v>Peas</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f5ff21a61ca453b"/>
+  </x:tableParts>
 </x:worksheet>
 </file>